--- a/reports/20260515/UI_BLOCK_UNBLOCK_FEEDBACK_ADMIN_PW.xlsx
+++ b/reports/20260515/UI_BLOCK_UNBLOCK_FEEDBACK_ADMIN_PW.xlsx
@@ -550,14 +550,14 @@
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
-          <t>75.18s</t>
+          <t>68.61s</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>09:07:34</t>
+          <t>09:31:10</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09:07:46</t>
+          <t>09:31:20</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>09:07:46</t>
+          <t>09:31:20</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>09:07:49</t>
+          <t>09:31:23</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>09:07:49</t>
+          <t>09:31:23</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>09:07:51</t>
+          <t>09:31:25</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -689,7 +689,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09:07:51</t>
+          <t>09:31:25</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>09:07:55</t>
+          <t>09:31:29</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>09:07:55</t>
+          <t>09:31:30</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>09:08:10</t>
+          <t>09:31:40</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>09:08:10</t>
+          <t>09:31:40</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>09:08:10</t>
+          <t>09:31:40</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>09:08:10</t>
+          <t>09:31:41</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>09:08:10</t>
+          <t>09:31:41</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -866,7 +866,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>09:08:12</t>
+          <t>09:31:42</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>09:08:12</t>
+          <t>09:31:43</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>09:08:14</t>
+          <t>09:31:44</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -933,7 +933,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>09:08:14</t>
+          <t>09:31:44</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>09:08:16</t>
+          <t>09:31:46</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -977,7 +977,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>09:08:16</t>
+          <t>09:31:46</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>09:08:24</t>
+          <t>09:31:53</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>09:08:24</t>
+          <t>09:31:53</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1043,7 +1043,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>09:08:26</t>
+          <t>09:31:56</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>09:08:32</t>
+          <t>09:32:02</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>09:08:48</t>
+          <t>09:32:17</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
